--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_character_create.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_character_create.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="140">
   <si>
     <t>唯一id</t>
   </si>
@@ -239,8 +239,63 @@
     </r>
   </si>
   <si>
-    <t>角色创建时所在的地点
-格式：地图id#X坐标#Y坐标</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色创建时所在的地点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>格式：地图</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>id#X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>坐标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>#Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>坐标</t>
+    </r>
   </si>
   <si>
     <t>格式：道具id#修正id|道具id#修正id
@@ -694,7 +749,7 @@
     <t>-60#-180#100</t>
   </si>
   <si>
-    <t>16</t>
+    <t>1052#47#225</t>
   </si>
   <si>
     <t>光明法师</t>
@@ -2009,7 +2064,7 @@
       <c r="N2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="P2" t="s">
@@ -2562,11 +2617,11 @@
       <c r="M10" t="s">
         <v>105</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N10">
+        <v>16</v>
+      </c>
+      <c r="O10" t="s">
         <v>135</v>
-      </c>
-      <c r="O10" t="s">
-        <v>81</v>
       </c>
       <c r="P10" t="s">
         <v>120</v>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_character_create.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_character_create.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_character_create" sheetId="1" r:id="rId1"/>
@@ -494,7 +494,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>剑士</t>
+    <t>Dark Knight</t>
   </si>
   <si>
     <t>Model/Face/newface02</t>
@@ -503,7 +503,7 @@
     <t>txt_swordMan</t>
   </si>
   <si>
-    <t>战士的王国，勇士的后代，以强硬的体力和剑术为本的近距离攻击型角色，具使用剑、斧、杖等多种武器的能力。</t>
+    <t>ThekingdomofwarriorsdescendantsofbraveheroesAmeleeorientedclassbuiltonformidablephysicalstrengthandswordsmanshipCapableofwieldingavarietyofweaponsincludingswordsaxesandpolearms KingdomofmagiciansbackerofArkaEndowedwithpowerfulmanaabletocastoffensivemagicfreely</t>
   </si>
   <si>
     <t>-68#-160#100</t>
@@ -539,7 +539,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>魔法师</t>
+    <t>Dark Wizard</t>
   </si>
   <si>
     <t>Model/Face/newface01</t>
@@ -551,7 +551,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>魔法师的王国，阿尔卡的后台，具有强势的法力，可以自由施放攻击魔法。</t>
+    <t>KingdomofmagiciansbackerofArkaEndowedwithpowerfulmanaabletocastoffensivemagicfreely</t>
   </si>
   <si>
     <t>-86#-175#100</t>
@@ -572,7 +572,7 @@
     <t>magic</t>
   </si>
   <si>
-    <t>弓箭手</t>
+    <t>Fairy Elf</t>
   </si>
   <si>
     <t>Model/Face/newface03</t>
@@ -581,7 +581,7 @@
     <t>txt_archer</t>
   </si>
   <si>
-    <t>精灵的王国，仙踪林的一员，主要武器是弓和弩，在组队的情况下她们的补助魔法和召唤魔法能起到不凡的作用哦。</t>
+    <t>KingdomofElvesdwellersofNoriaTheirprimaryweaponsarebowsandcrossbowsWheninpartiestheirsupportandsummoningmagicplayanextraordinaryrole</t>
   </si>
   <si>
     <t>-67#-189#100</t>
@@ -614,7 +614,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>魔剑士</t>
+    <t>Magic Gladiator</t>
   </si>
   <si>
     <r>
@@ -646,7 +646,7 @@
     <t>Model/Face/newface04</t>
   </si>
   <si>
-    <t>是复合型角色，既有战士的勇气也具魔法师的智慧，不但可以使用近距离攻击还可以自由施放多种魔法。</t>
+    <t>AhybridtypeclasspossessingthecourageofwarriorsandthewisdomofmagiciansItcanperformmeleeattacksaswellasfreelycastvariouskindsofmagic</t>
   </si>
   <si>
     <t>-60#-150#100</t>
@@ -664,7 +664,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>圣导师</t>
+    <t>Dark Lord</t>
   </si>
   <si>
     <r>
@@ -696,7 +696,7 @@
     <t>Model/Face/newface05</t>
   </si>
   <si>
-    <t>具强势的号召力的君主型角色，用超强的统帅能力组织团队，身边还有可以补助攻击的天鹰和黑王马做自己的宠物。</t>
+    <t>AmonarchstyleclasswithpowerfulcharismaItorganizespartieswithsupremeleadershipaccompaniedbypetsDarkHawkandBlackKingHorsethatassistincombat</t>
   </si>
   <si>
     <t>-60#-160#100</t>
@@ -711,7 +711,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>召唤师</t>
+    <t>Summoner</t>
   </si>
   <si>
     <r>
@@ -743,7 +743,7 @@
     <t>Model/Face/newface06</t>
   </si>
   <si>
-    <t>以强大的精神与观察力使用诅咒的魔法，可以召唤异界的召唤兽使用强大的魔法。</t>
+    <t>Wieldingcursemagicwithpowerfulspiritandinsightitcansummonotherworldlycreaturestocastformidablespells</t>
   </si>
   <si>
     <t>-60#-180#100</t>
@@ -752,13 +752,13 @@
     <t>1052#47#225</t>
   </si>
   <si>
-    <t>光明法师</t>
+    <t>Light Wizard</t>
   </si>
   <si>
     <t>Model/Face/newface01_guangming</t>
   </si>
   <si>
-    <t>拥有了作为“光明法师”以及“圣光学者”的特性以及拥有善良、公正的头脑，擅长远距离作战，光明系魔法。</t>
+    <t>PossessingthetraitsofbothLightMageandHolyScholarblessedwithakindandimpartialmindSpecializesinlongrangecombatandlightattributemagic</t>
   </si>
   <si>
     <t>20020017#20050017#20090022#20110080#20150057</t>
@@ -1391,7 +1391,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1399,6 +1399,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2244,7 +2245,7 @@
       <c r="A5" t="s">
         <v>72</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>73</v>
       </c>
       <c r="C5" t="s">
@@ -2265,13 +2266,13 @@
       <c r="H5" t="s">
         <v>72</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="5" t="s">
         <v>76</v>
       </c>
       <c r="J5" t="s">
         <v>72</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>77</v>
       </c>
       <c r="L5" t="s">
@@ -2312,7 +2313,7 @@
       <c r="A6" t="s">
         <v>87</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>88</v>
       </c>
       <c r="C6" t="s">
@@ -2333,13 +2334,13 @@
       <c r="H6" t="s">
         <v>91</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="5" t="s">
         <v>92</v>
       </c>
       <c r="J6" t="s">
         <v>72</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="7" t="s">
         <v>93</v>
       </c>
       <c r="L6" t="s">
@@ -2374,7 +2375,7 @@
       <c r="A7" t="s">
         <v>91</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
         <v>99</v>
       </c>
       <c r="C7" t="s">
@@ -2395,13 +2396,13 @@
       <c r="H7" t="s">
         <v>87</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="5" t="s">
         <v>102</v>
       </c>
       <c r="J7" t="s">
         <v>72</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>103</v>
       </c>
       <c r="L7" t="s">
@@ -2442,7 +2443,7 @@
       <c r="A8" t="s">
         <v>112</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -2460,13 +2461,13 @@
       <c r="H8" t="s">
         <v>25</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="6">
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="7" t="s">
         <v>117</v>
       </c>
       <c r="L8" t="s">
@@ -2513,7 +2514,7 @@
       <c r="A9" t="s">
         <v>121</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
         <v>122</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2531,13 +2532,13 @@
       <c r="H9" t="s">
         <v>25</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="6">
         <v>1</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="7" t="s">
         <v>126</v>
       </c>
       <c r="L9" t="s">
@@ -2584,7 +2585,7 @@
       <c r="A10" t="s">
         <v>129</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>130</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2602,13 +2603,13 @@
       <c r="H10" t="s">
         <v>25</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="6">
         <v>1</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="7" t="s">
         <v>134</v>
       </c>
       <c r="L10" t="s">
@@ -2655,7 +2656,7 @@
       <c r="A11">
         <v>7</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="5" t="s">
         <v>136</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -2667,13 +2668,13 @@
       <c r="G11" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="5" t="s">
         <v>138</v>
       </c>
       <c r="J11" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="7" t="s">
         <v>77</v>
       </c>
       <c r="L11" t="s">
